--- a/ARM Functions/Ability Edits/Wonder Skin.xlsx
+++ b/ARM Functions/Ability Edits/Wonder Skin.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\ROM\3ds\Modded ROM\USUM ARM research\Ability Edits\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\ROM\3ds\USUM ARM research\Ability Edits\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FEFB290-045D-40D7-BDB9-3D5D8E4A6D29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E00FDD9B-98DB-4F63-A7A6-E80078698698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3615" yWindow="3615" windowWidth="21600" windowHeight="11422" xr2:uid="{664BA6B8-043A-4EF3-A83B-BDEF02BD0490}"/>
+    <workbookView xWindow="-29263" yWindow="5734" windowWidth="24686" windowHeight="12497" xr2:uid="{664BA6B8-043A-4EF3-A83B-BDEF02BD0490}"/>
   </bookViews>
   <sheets>
     <sheet name="Wonder Skin" sheetId="1" r:id="rId1"/>
@@ -131,9 +131,6 @@
     <t>000D7D50</t>
   </si>
   <si>
-    <t>Main</t>
-  </si>
-  <si>
     <t>notes</t>
   </si>
   <si>
@@ -144,13 +141,16 @@
   </si>
   <si>
     <t>Address</t>
+  </si>
+  <si>
+    <t>Main 0x41</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -534,38 +534,38 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC3FF682-529F-445E-A539-EDFF7BE80E58}">
   <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.15"/>
   <cols>
-    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.35546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.73046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24" customWidth="1"/>
-    <col min="9" max="11" width="2.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="2.35546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6">
       <c r="A1" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="4" t="s">
         <v>35</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A2" s="4" t="s">
-        <v>31</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6">
       <c r="A3" s="3" t="s">
         <v>30</v>
       </c>
@@ -576,9 +576,9 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:6">
       <c r="A4" t="str">
-        <f>DEC2HEX(HEX2DEC(A3)+4,8)</f>
+        <f t="shared" ref="A4:A21" si="0">DEC2HEX(HEX2DEC(A3)+4,8)</f>
         <v>000D7D54</v>
       </c>
       <c r="B4" t="s">
@@ -588,9 +588,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:6">
       <c r="A5" t="str">
-        <f>DEC2HEX(HEX2DEC(A4)+4,8)</f>
+        <f t="shared" si="0"/>
         <v>000D7D58</v>
       </c>
       <c r="B5" t="s">
@@ -600,9 +600,9 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:6">
       <c r="A6" t="str">
-        <f>DEC2HEX(HEX2DEC(A5)+4,8)</f>
+        <f t="shared" si="0"/>
         <v>000D7D5C</v>
       </c>
       <c r="B6" t="s">
@@ -612,9 +612,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:6">
       <c r="A7" t="str">
-        <f>DEC2HEX(HEX2DEC(A6)+4,8)</f>
+        <f t="shared" si="0"/>
         <v>000D7D60</v>
       </c>
       <c r="B7" s="3" t="s">
@@ -624,9 +624,9 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:6">
       <c r="A8" t="str">
-        <f>DEC2HEX(HEX2DEC(A7)+4,8)</f>
+        <f t="shared" si="0"/>
         <v>000D7D64</v>
       </c>
       <c r="B8" s="3" t="s">
@@ -638,9 +638,9 @@
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:6">
       <c r="A9" t="str">
-        <f>DEC2HEX(HEX2DEC(A8)+4,8)</f>
+        <f t="shared" si="0"/>
         <v>000D7D68</v>
       </c>
       <c r="B9" s="1" t="s">
@@ -652,9 +652,9 @@
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:6">
       <c r="A10" t="str">
-        <f>DEC2HEX(HEX2DEC(A9)+4,8)</f>
+        <f t="shared" si="0"/>
         <v>000D7D6C</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -666,9 +666,9 @@
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:6">
       <c r="A11" t="str">
-        <f>DEC2HEX(HEX2DEC(A10)+4,8)</f>
+        <f t="shared" si="0"/>
         <v>000D7D70</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -680,9 +680,9 @@
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:6">
       <c r="A12" t="str">
-        <f>DEC2HEX(HEX2DEC(A11)+4,8)</f>
+        <f t="shared" si="0"/>
         <v>000D7D74</v>
       </c>
       <c r="B12" s="1" t="s">
@@ -693,9 +693,9 @@
       </c>
       <c r="F12" s="2"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:6">
       <c r="A13" t="str">
-        <f>DEC2HEX(HEX2DEC(A12)+4,8)</f>
+        <f t="shared" si="0"/>
         <v>000D7D78</v>
       </c>
       <c r="B13" s="1" t="s">
@@ -707,9 +707,9 @@
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:6">
       <c r="A14" t="str">
-        <f>DEC2HEX(HEX2DEC(A13)+4,8)</f>
+        <f t="shared" si="0"/>
         <v>000D7D7C</v>
       </c>
       <c r="B14" t="s">
@@ -719,9 +719,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:6">
       <c r="A15" t="str">
-        <f>DEC2HEX(HEX2DEC(A14)+4,8)</f>
+        <f t="shared" si="0"/>
         <v>000D7D80</v>
       </c>
       <c r="B15" s="3" t="s">
@@ -731,9 +731,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:6">
       <c r="A16" t="str">
-        <f>DEC2HEX(HEX2DEC(A15)+4,8)</f>
+        <f t="shared" si="0"/>
         <v>000D7D84</v>
       </c>
       <c r="B16" s="3" t="s">
@@ -743,9 +743,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:6">
       <c r="A17" t="str">
-        <f>DEC2HEX(HEX2DEC(A16)+4,8)</f>
+        <f t="shared" si="0"/>
         <v>000D7D88</v>
       </c>
       <c r="B17" s="3" t="s">
@@ -755,9 +755,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:6">
       <c r="A18" t="str">
-        <f>DEC2HEX(HEX2DEC(A17)+4,8)</f>
+        <f t="shared" si="0"/>
         <v>000D7D8C</v>
       </c>
       <c r="B18" s="3" t="s">
@@ -767,9 +767,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:6">
       <c r="A19" t="str">
-        <f>DEC2HEX(HEX2DEC(A18)+4,8)</f>
+        <f t="shared" si="0"/>
         <v>000D7D90</v>
       </c>
       <c r="B19" s="1" t="s">
@@ -780,9 +780,9 @@
       </c>
       <c r="D19" s="1"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:6">
       <c r="A20" t="str">
-        <f>DEC2HEX(HEX2DEC(A19)+4,8)</f>
+        <f t="shared" si="0"/>
         <v>000D7D94</v>
       </c>
       <c r="B20" t="s">
@@ -794,9 +794,9 @@
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:6">
       <c r="A21" t="str">
-        <f>DEC2HEX(HEX2DEC(A20)+4,8)</f>
+        <f t="shared" si="0"/>
         <v>000D7D98</v>
       </c>
       <c r="B21" s="1" t="s">
